--- a/gom-ai/experiment_results/thuc_nghiem_dataset1_chinh_xac.xlsx
+++ b/gom-ai/experiment_results/thuc_nghiem_dataset1_chinh_xac.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,6 +68,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00008000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="008B0000"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -135,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -172,6 +178,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -641,32 +650,32 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>64.03%</t>
+          <t>56.86%</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>62.00%</t>
+          <t>40.00%</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>62.44%</t>
+          <t>41.13%</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>1.475s</t>
+          <t>7.024s</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>14.0%</t>
         </is>
       </c>
     </row>
@@ -683,32 +692,32 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>61.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>55.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>56.35%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>1.151s</t>
+          <t>2.743s</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -725,32 +734,32 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>59.69%</t>
+          <t>49.21%</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>58.00%</t>
+          <t>28.57%</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>57.96%</t>
+          <t>31.00%</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>0.683s</t>
+          <t>3.764s</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>23.0%</t>
         </is>
       </c>
     </row>
@@ -772,27 +781,27 @@
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>94.27%</t>
+          <t>68.49%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>92.00%</t>
+          <t>65.71%</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>93.04%</t>
+          <t>64.81%</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>14.212s</t>
+          <t>20.304s</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>1.0%</t>
         </is>
       </c>
     </row>
@@ -817,22 +826,22 @@
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>+30.00%</t>
+          <t>+36.00%</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>+30.24%</t>
+          <t>+11.63%</t>
         </is>
       </c>
       <c r="E12" s="16" t="inlineStr">
         <is>
-          <t>+30.00%</t>
+          <t>+25.71%</t>
         </is>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>+30.60%</t>
+          <t>+23.68%</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
@@ -842,7 +851,7 @@
       </c>
       <c r="H12" s="16" t="inlineStr">
         <is>
-          <t>-3.00%</t>
+          <t>-13.00%</t>
         </is>
       </c>
     </row>
@@ -859,22 +868,22 @@
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>+37.00%</t>
+          <t>+92.00%</t>
         </is>
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>+33.27%</t>
+          <t>+68.49%</t>
         </is>
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
-          <t>+37.00%</t>
+          <t>+65.71%</t>
         </is>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>+36.69%</t>
+          <t>+64.81%</t>
         </is>
       </c>
       <c r="G13" s="17" t="inlineStr">
@@ -882,9 +891,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>-2.00%</t>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>+1.00%</t>
         </is>
       </c>
     </row>
@@ -901,22 +910,22 @@
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>+34.00%</t>
+          <t>+52.00%</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>+34.58%</t>
+          <t>+19.28%</t>
         </is>
       </c>
       <c r="E14" s="16" t="inlineStr">
         <is>
-          <t>+34.00%</t>
+          <t>+37.14%</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>+35.08%</t>
+          <t>+33.81%</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr">
@@ -926,7 +935,7 @@
       </c>
       <c r="H14" s="16" t="inlineStr">
         <is>
-          <t>-3.00%</t>
+          <t>-22.00%</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1050,7 @@
           <t>Bat Trang</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -1051,27 +1060,27 @@
           <t>Bat Trang</t>
         </is>
       </c>
-      <c r="G4" s="19" t="inlineStr">
+      <c r="G4" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>Goryeo Celadon</t>
-        </is>
-      </c>
-      <c r="I4" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I4" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="J4" s="9" t="inlineStr">
         <is>
-          <t>Bau Truc</t>
-        </is>
-      </c>
-      <c r="K4" s="20" t="inlineStr">
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="K4" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -1096,7 +1105,7 @@
           <t>Bat Trang</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -1106,17 +1115,17 @@
           <t>Bat Trang</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>Delftware</t>
-        </is>
-      </c>
-      <c r="I5" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -1126,7 +1135,7 @@
           <t>Bat Trang</t>
         </is>
       </c>
-      <c r="K5" s="19" t="inlineStr">
+      <c r="K5" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -1151,19 +1160,19 @@
           <t>Bat Trang</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Không xác định</t>
+          <t>Bat Trang</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
@@ -1171,7 +1180,7 @@
           <t>Không xác định</t>
         </is>
       </c>
-      <c r="I6" s="20" t="inlineStr">
+      <c r="I6" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -1181,7 +1190,7 @@
           <t>Bat Trang</t>
         </is>
       </c>
-      <c r="K6" s="19" t="inlineStr">
+      <c r="K6" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -1206,37 +1215,37 @@
           <t>Bat Trang</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>Delftware</t>
+          <t>Bat Trang</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>Bat Trang</t>
-        </is>
-      </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>Delftware</t>
-        </is>
-      </c>
-      <c r="K7" s="20" t="inlineStr">
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -1261,7 +1270,7 @@
           <t>Bat Trang</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -1271,27 +1280,27 @@
           <t>Bat Trang</t>
         </is>
       </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>Bat Trang</t>
-        </is>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J8" s="9" t="inlineStr">
         <is>
-          <t>Arita Imari</t>
-        </is>
-      </c>
-      <c r="K8" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="K8" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -1316,29 +1325,29 @@
           <t>Bat Trang</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>Goryeo Celadon</t>
+          <t>Bat Trang</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>Bat Trang</t>
-        </is>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
@@ -1346,7 +1355,7 @@
           <t>Bat Trang</t>
         </is>
       </c>
-      <c r="K9" s="19" t="inlineStr">
+      <c r="K9" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -1371,7 +1380,7 @@
           <t>Bat Trang</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -1381,27 +1390,27 @@
           <t>Bat Trang</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>Bat Trang</t>
-        </is>
-      </c>
-      <c r="I10" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
-          <t>Delftware</t>
-        </is>
-      </c>
-      <c r="K10" s="20" t="inlineStr">
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="K10" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -1426,7 +1435,7 @@
           <t>Bat Trang</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -1436,27 +1445,27 @@
           <t>Bat Trang</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>Bat Trang</t>
-        </is>
-      </c>
-      <c r="I11" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>Không xác định</t>
-        </is>
-      </c>
-      <c r="K11" s="20" t="inlineStr">
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="K11" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -1481,7 +1490,7 @@
           <t>Bat Trang</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -1491,29 +1500,29 @@
           <t>Bat Trang</t>
         </is>
       </c>
-      <c r="G12" s="19" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>Bat Trang</t>
-        </is>
-      </c>
-      <c r="I12" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J12" s="9" t="inlineStr">
         <is>
-          <t>Iznik</t>
+          <t>Bat Trang</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1545,7 @@
           <t>Bat Trang</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E13" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -1546,29 +1555,29 @@
           <t>Bat Trang</t>
         </is>
       </c>
-      <c r="G13" s="19" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>Chu Dau</t>
-        </is>
-      </c>
-      <c r="I13" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>Bat Trang</t>
-        </is>
-      </c>
-      <c r="K13" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Jingdezhen</t>
+        </is>
+      </c>
+      <c r="K13" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -1591,29 +1600,29 @@
           <t>Bau Truc</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E14" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>Không xác định</t>
+          <t>Bau Truc</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>Bau Truc</t>
-        </is>
-      </c>
-      <c r="I14" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J14" s="9" t="inlineStr">
@@ -1621,7 +1630,7 @@
           <t>Phu Lang</t>
         </is>
       </c>
-      <c r="K14" s="20" t="inlineStr">
+      <c r="K14" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -1646,39 +1655,39 @@
           <t>Bau Truc</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="E15" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>Goryeo Celadon</t>
+          <t>Bau Truc</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
           <t>Phu Lang</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr">
-        <is>
-          <t>SAI</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>Bau Truc</t>
-        </is>
-      </c>
-      <c r="K15" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+      <c r="K15" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -1701,39 +1710,39 @@
           <t>Bau Truc</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Bau Truc</t>
-        </is>
-      </c>
-      <c r="G16" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>Bau Truc</t>
-        </is>
-      </c>
-      <c r="I16" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
-          <t>Bau Truc</t>
-        </is>
-      </c>
-      <c r="K16" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="K16" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -1756,39 +1765,39 @@
           <t>Bau Truc</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E17" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>Bau Truc</t>
-        </is>
-      </c>
-      <c r="G17" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>Meissen</t>
-        </is>
-      </c>
-      <c r="I17" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>Bau Truc</t>
-        </is>
-      </c>
-      <c r="K17" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="K17" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -1811,29 +1820,29 @@
           <t>Bau Truc</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Bau Truc</t>
-        </is>
-      </c>
-      <c r="G18" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>Bau Truc</t>
-        </is>
-      </c>
-      <c r="I18" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
@@ -1841,7 +1850,7 @@
           <t>Không xác định</t>
         </is>
       </c>
-      <c r="K18" s="20" t="inlineStr">
+      <c r="K18" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -1866,39 +1875,39 @@
           <t>Bau Truc</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="E19" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>Bau Truc</t>
-        </is>
-      </c>
-      <c r="G19" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>Chu Dau</t>
-        </is>
-      </c>
-      <c r="I19" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>Bau Truc</t>
-        </is>
-      </c>
-      <c r="K19" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="K19" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -1921,37 +1930,37 @@
           <t>Bau Truc</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E20" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Bau Truc</t>
-        </is>
-      </c>
-      <c r="G20" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>Bau Truc</t>
-        </is>
-      </c>
-      <c r="I20" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>Arita Imari</t>
-        </is>
-      </c>
-      <c r="K20" s="20" t="inlineStr">
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="K20" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -1976,7 +1985,7 @@
           <t>Bau Truc</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="E21" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -1986,29 +1995,29 @@
           <t>Không xác định</t>
         </is>
       </c>
-      <c r="G21" s="20" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>Bau Truc</t>
-        </is>
-      </c>
-      <c r="I21" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>Bau Truc</t>
-        </is>
-      </c>
-      <c r="K21" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="K21" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -2031,39 +2040,39 @@
           <t>Bau Truc</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="E22" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>Bau Truc</t>
-        </is>
-      </c>
-      <c r="G22" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>Bau Truc</t>
-        </is>
-      </c>
-      <c r="I22" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>Bau Truc</t>
-        </is>
-      </c>
-      <c r="K22" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="K22" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -2086,39 +2095,39 @@
           <t>Bau Truc</t>
         </is>
       </c>
-      <c r="E23" s="18" t="inlineStr">
+      <c r="E23" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>Iznik</t>
-        </is>
-      </c>
-      <c r="G23" s="20" t="inlineStr">
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
           <t>Phu Lang</t>
         </is>
       </c>
-      <c r="I23" s="20" t="inlineStr">
-        <is>
-          <t>SAI</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="inlineStr">
-        <is>
-          <t>Bau Truc</t>
-        </is>
-      </c>
-      <c r="K23" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+      <c r="K23" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2150,7 @@
           <t>Phu Lang</t>
         </is>
       </c>
-      <c r="E24" s="18" t="inlineStr">
+      <c r="E24" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -2151,27 +2160,27 @@
           <t>Phu Lang</t>
         </is>
       </c>
-      <c r="G24" s="19" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
           <t>Phu Lang</t>
         </is>
       </c>
-      <c r="I24" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="J24" s="9" t="inlineStr">
-        <is>
-          <t>Phu Lang</t>
-        </is>
-      </c>
-      <c r="K24" s="19" t="inlineStr">
+      <c r="K24" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -2196,39 +2205,39 @@
           <t>Phu Lang</t>
         </is>
       </c>
-      <c r="E25" s="18" t="inlineStr">
+      <c r="E25" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
           <t>Phu Lang</t>
         </is>
       </c>
-      <c r="G25" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="H25" s="9" t="inlineStr">
-        <is>
-          <t>Chu Dau</t>
-        </is>
-      </c>
-      <c r="I25" s="20" t="inlineStr">
-        <is>
-          <t>SAI</t>
-        </is>
-      </c>
-      <c r="J25" s="9" t="inlineStr">
-        <is>
-          <t>Chu Dau</t>
-        </is>
-      </c>
       <c r="K25" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2260,7 @@
           <t>Phu Lang</t>
         </is>
       </c>
-      <c r="E26" s="18" t="inlineStr">
+      <c r="E26" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -2261,29 +2270,29 @@
           <t>Phu Lang</t>
         </is>
       </c>
-      <c r="G26" s="19" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
           <t>Phu Lang</t>
         </is>
       </c>
-      <c r="I26" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="J26" s="9" t="inlineStr">
-        <is>
-          <t>Delftware</t>
-        </is>
-      </c>
       <c r="K26" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
     </row>
@@ -2306,37 +2315,37 @@
           <t>Phu Lang</t>
         </is>
       </c>
-      <c r="E27" s="18" t="inlineStr">
+      <c r="E27" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
+          <t>Bau Truc</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="inlineStr">
+        <is>
           <t>Phu Lang</t>
         </is>
       </c>
-      <c r="G27" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="H27" s="9" t="inlineStr">
-        <is>
-          <t>Phu Lang</t>
-        </is>
-      </c>
-      <c r="I27" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="J27" s="9" t="inlineStr">
-        <is>
-          <t>Phu Lang</t>
-        </is>
-      </c>
-      <c r="K27" s="19" t="inlineStr">
+      <c r="K27" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -2361,39 +2370,39 @@
           <t>Phu Lang</t>
         </is>
       </c>
-      <c r="E28" s="18" t="inlineStr">
+      <c r="E28" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
           <t>Phu Lang</t>
         </is>
       </c>
-      <c r="G28" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="H28" s="9" t="inlineStr">
-        <is>
-          <t>Phu Lang</t>
-        </is>
-      </c>
-      <c r="I28" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="J28" s="9" t="inlineStr">
-        <is>
-          <t>Delftware</t>
-        </is>
-      </c>
       <c r="K28" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
     </row>
@@ -2416,39 +2425,39 @@
           <t>Phu Lang</t>
         </is>
       </c>
-      <c r="E29" s="18" t="inlineStr">
+      <c r="E29" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
           <t>Phu Lang</t>
         </is>
       </c>
-      <c r="G29" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="H29" s="9" t="inlineStr">
-        <is>
-          <t>Phu Lang</t>
-        </is>
-      </c>
-      <c r="I29" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="inlineStr">
-        <is>
-          <t>Bien Hoa</t>
-        </is>
-      </c>
       <c r="K29" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
     </row>
@@ -2468,42 +2477,42 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Iznik</t>
-        </is>
-      </c>
-      <c r="E30" s="21" t="inlineStr">
-        <is>
-          <t>SAI</t>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
           <t>Phu Lang</t>
         </is>
       </c>
-      <c r="G30" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t>Bau Truc</t>
-        </is>
-      </c>
-      <c r="I30" s="20" t="inlineStr">
-        <is>
-          <t>SAI</t>
-        </is>
-      </c>
-      <c r="J30" s="9" t="inlineStr">
-        <is>
-          <t>Bien Hoa</t>
-        </is>
-      </c>
       <c r="K30" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
     </row>
@@ -2526,39 +2535,39 @@
           <t>Phu Lang</t>
         </is>
       </c>
-      <c r="E31" s="18" t="inlineStr">
+      <c r="E31" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
           <t>Phu Lang</t>
         </is>
       </c>
-      <c r="G31" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="H31" s="9" t="inlineStr">
-        <is>
-          <t>Phu Lang</t>
-        </is>
-      </c>
-      <c r="I31" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="J31" s="9" t="inlineStr">
-        <is>
-          <t>Iznik</t>
-        </is>
-      </c>
       <c r="K31" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
     </row>
@@ -2578,42 +2587,42 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Arita Imari</t>
-        </is>
-      </c>
-      <c r="E32" s="21" t="inlineStr">
-        <is>
-          <t>SAI</t>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>Phu Lang</t>
-        </is>
-      </c>
-      <c r="G32" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>Phu Lang</t>
-        </is>
-      </c>
-      <c r="I32" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>Phu Lang</t>
-        </is>
-      </c>
-      <c r="K32" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="K32" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -2636,37 +2645,37 @@
           <t>Phu Lang</t>
         </is>
       </c>
-      <c r="E33" s="18" t="inlineStr">
+      <c r="E33" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>Phu Lang</t>
-        </is>
-      </c>
-      <c r="G33" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="G33" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>Phu Lang</t>
-        </is>
-      </c>
-      <c r="I33" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I33" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>Bau Truc</t>
-        </is>
-      </c>
-      <c r="K33" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="K33" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -2691,27 +2700,27 @@
           <t>Bien Hoa</t>
         </is>
       </c>
-      <c r="E34" s="18" t="inlineStr">
+      <c r="E34" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>Meissen</t>
-        </is>
-      </c>
-      <c r="G34" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="G34" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>Arita Imari</t>
-        </is>
-      </c>
-      <c r="I34" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I34" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -2721,7 +2730,7 @@
           <t>Phu Lang</t>
         </is>
       </c>
-      <c r="K34" s="20" t="inlineStr">
+      <c r="K34" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -2746,37 +2755,37 @@
           <t>Bien Hoa</t>
         </is>
       </c>
-      <c r="E35" s="18" t="inlineStr">
+      <c r="E35" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>Bien Hoa</t>
-        </is>
-      </c>
-      <c r="G35" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G35" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>Chu Dau</t>
-        </is>
-      </c>
-      <c r="I35" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I35" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>Chu Dau</t>
-        </is>
-      </c>
-      <c r="K35" s="20" t="inlineStr">
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="K35" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -2801,37 +2810,37 @@
           <t>Bien Hoa</t>
         </is>
       </c>
-      <c r="E36" s="18" t="inlineStr">
+      <c r="E36" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>Bien Hoa</t>
-        </is>
-      </c>
-      <c r="G36" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G36" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>Bien Hoa</t>
-        </is>
-      </c>
-      <c r="I36" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I36" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>Meissen</t>
-        </is>
-      </c>
-      <c r="K36" s="20" t="inlineStr">
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="K36" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -2856,37 +2865,37 @@
           <t>Bien Hoa</t>
         </is>
       </c>
-      <c r="E37" s="18" t="inlineStr">
+      <c r="E37" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>Bien Hoa</t>
-        </is>
-      </c>
-      <c r="G37" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G37" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>Bien Hoa</t>
-        </is>
-      </c>
-      <c r="I37" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I37" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>Bat Trang</t>
-        </is>
-      </c>
-      <c r="K37" s="20" t="inlineStr">
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="K37" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -2911,19 +2920,19 @@
           <t>Bien Hoa</t>
         </is>
       </c>
-      <c r="E38" s="18" t="inlineStr">
+      <c r="E38" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>Bien Hoa</t>
-        </is>
-      </c>
-      <c r="G38" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G38" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="H38" s="9" t="inlineStr">
@@ -2931,19 +2940,19 @@
           <t>Không xác định</t>
         </is>
       </c>
-      <c r="I38" s="20" t="inlineStr">
+      <c r="I38" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>Bien Hoa</t>
-        </is>
-      </c>
-      <c r="K38" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="K38" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -2966,37 +2975,37 @@
           <t>Bien Hoa</t>
         </is>
       </c>
-      <c r="E39" s="18" t="inlineStr">
+      <c r="E39" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>Bien Hoa</t>
-        </is>
-      </c>
-      <c r="G39" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G39" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
-          <t>Bien Hoa</t>
-        </is>
-      </c>
-      <c r="I39" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I39" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J39" s="9" t="inlineStr">
         <is>
-          <t>Chu Dau</t>
-        </is>
-      </c>
-      <c r="K39" s="20" t="inlineStr">
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="K39" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -3021,37 +3030,37 @@
           <t>Bien Hoa</t>
         </is>
       </c>
-      <c r="E40" s="18" t="inlineStr">
+      <c r="E40" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="G40" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I40" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
           <t>Phu Lang</t>
         </is>
       </c>
-      <c r="G40" s="20" t="inlineStr">
-        <is>
-          <t>SAI</t>
-        </is>
-      </c>
-      <c r="H40" s="9" t="inlineStr">
-        <is>
-          <t>Bien Hoa</t>
-        </is>
-      </c>
-      <c r="I40" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="J40" s="9" t="inlineStr">
-        <is>
-          <t>Không xác định</t>
-        </is>
-      </c>
-      <c r="K40" s="20" t="inlineStr">
+      <c r="K40" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -3076,37 +3085,37 @@
           <t>Bien Hoa</t>
         </is>
       </c>
-      <c r="E41" s="18" t="inlineStr">
+      <c r="E41" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>Bien Hoa</t>
-        </is>
-      </c>
-      <c r="G41" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G41" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
-          <t>Bien Hoa</t>
-        </is>
-      </c>
-      <c r="I41" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I41" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>Bat Trang</t>
-        </is>
-      </c>
-      <c r="K41" s="20" t="inlineStr">
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="K41" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -3131,39 +3140,39 @@
           <t>Bien Hoa</t>
         </is>
       </c>
-      <c r="E42" s="18" t="inlineStr">
+      <c r="E42" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>Phu Lang</t>
-        </is>
-      </c>
-      <c r="G42" s="20" t="inlineStr">
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G42" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
-          <t>Bien Hoa</t>
-        </is>
-      </c>
-      <c r="I42" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I42" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>Bien Hoa</t>
-        </is>
-      </c>
-      <c r="K42" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Jingdezhen</t>
+        </is>
+      </c>
+      <c r="K42" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -3183,40 +3192,40 @@
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Phu Lang</t>
-        </is>
-      </c>
-      <c r="E43" s="21" t="inlineStr">
-        <is>
-          <t>SAI</t>
+          <t>Bien Hoa</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>Chu Dau</t>
-        </is>
-      </c>
-      <c r="G43" s="20" t="inlineStr">
+          <t>Jingdezhen</t>
+        </is>
+      </c>
+      <c r="G43" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="H43" s="9" t="inlineStr">
         <is>
-          <t>Goryeo Celadon</t>
-        </is>
-      </c>
-      <c r="I43" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I43" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>Phu Lang</t>
-        </is>
-      </c>
-      <c r="K43" s="20" t="inlineStr">
+          <t>Jingdezhen</t>
+        </is>
+      </c>
+      <c r="K43" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -3241,37 +3250,37 @@
           <t>Chu Dau</t>
         </is>
       </c>
-      <c r="E44" s="18" t="inlineStr">
+      <c r="E44" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F44" s="9" t="inlineStr">
         <is>
-          <t>Bat Trang</t>
+          <t>Chu Dau</t>
         </is>
       </c>
       <c r="G44" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H44" s="9" t="inlineStr">
         <is>
-          <t>Delftware</t>
-        </is>
-      </c>
-      <c r="I44" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I44" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>Bat Trang</t>
-        </is>
-      </c>
-      <c r="K44" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="K44" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -3296,39 +3305,39 @@
           <t>Chu Dau</t>
         </is>
       </c>
-      <c r="E45" s="18" t="inlineStr">
+      <c r="E45" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>Arita Imari</t>
+          <t>Chu Dau</t>
         </is>
       </c>
       <c r="G45" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H45" s="9" t="inlineStr">
         <is>
-          <t>Chu Dau</t>
-        </is>
-      </c>
-      <c r="I45" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I45" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J45" s="9" t="inlineStr">
         <is>
-          <t>Chu Dau</t>
-        </is>
-      </c>
-      <c r="K45" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="K45" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3360,7 @@
           <t>Chu Dau</t>
         </is>
       </c>
-      <c r="E46" s="18" t="inlineStr">
+      <c r="E46" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -3361,29 +3370,29 @@
           <t>Chu Dau</t>
         </is>
       </c>
-      <c r="G46" s="19" t="inlineStr">
+      <c r="G46" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H46" s="9" t="inlineStr">
         <is>
-          <t>Bien Hoa</t>
-        </is>
-      </c>
-      <c r="I46" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I46" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>Iznik</t>
+          <t>Chu Dau</t>
         </is>
       </c>
       <c r="K46" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3415,7 @@
           <t>Chu Dau</t>
         </is>
       </c>
-      <c r="E47" s="18" t="inlineStr">
+      <c r="E47" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -3416,7 +3425,7 @@
           <t>Chu Dau</t>
         </is>
       </c>
-      <c r="G47" s="19" t="inlineStr">
+      <c r="G47" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -3426,19 +3435,19 @@
           <t>Không xác định</t>
         </is>
       </c>
-      <c r="I47" s="20" t="inlineStr">
+      <c r="I47" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="J47" s="9" t="inlineStr">
         <is>
-          <t>Chu Dau</t>
-        </is>
-      </c>
-      <c r="K47" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="K47" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3470,7 @@
           <t>Chu Dau</t>
         </is>
       </c>
-      <c r="E48" s="18" t="inlineStr">
+      <c r="E48" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -3471,29 +3480,29 @@
           <t>Chu Dau</t>
         </is>
       </c>
-      <c r="G48" s="19" t="inlineStr">
+      <c r="G48" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H48" s="9" t="inlineStr">
         <is>
-          <t>Bat Trang</t>
-        </is>
-      </c>
-      <c r="I48" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I48" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>Chu Dau</t>
-        </is>
-      </c>
-      <c r="K48" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="K48" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -3516,39 +3525,39 @@
           <t>Chu Dau</t>
         </is>
       </c>
-      <c r="E49" s="18" t="inlineStr">
+      <c r="E49" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>Bien Hoa</t>
+          <t>Chu Dau</t>
         </is>
       </c>
       <c r="G49" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H49" s="9" t="inlineStr">
         <is>
-          <t>Chu Dau</t>
-        </is>
-      </c>
-      <c r="I49" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I49" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J49" s="9" t="inlineStr">
         <is>
-          <t>Chu Dau</t>
-        </is>
-      </c>
-      <c r="K49" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="K49" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -3568,12 +3577,12 @@
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Meissen</t>
-        </is>
-      </c>
-      <c r="E50" s="21" t="inlineStr">
-        <is>
-          <t>SAI</t>
+          <t>Chu Dau</t>
+        </is>
+      </c>
+      <c r="E50" s="19" t="inlineStr">
+        <is>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F50" s="9" t="inlineStr">
@@ -3581,29 +3590,29 @@
           <t>Chu Dau</t>
         </is>
       </c>
-      <c r="G50" s="19" t="inlineStr">
+      <c r="G50" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H50" s="9" t="inlineStr">
         <is>
-          <t>Bien Hoa</t>
-        </is>
-      </c>
-      <c r="I50" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I50" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
-          <t>Chu Dau</t>
-        </is>
-      </c>
-      <c r="K50" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="K50" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -3626,37 +3635,37 @@
           <t>Chu Dau</t>
         </is>
       </c>
-      <c r="E51" s="18" t="inlineStr">
+      <c r="E51" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>Goryeo Celadon</t>
+          <t>Chu Dau</t>
         </is>
       </c>
       <c r="G51" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
-          <t>Chu Dau</t>
-        </is>
-      </c>
-      <c r="I51" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I51" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J51" s="9" t="inlineStr">
         <is>
-          <t>Arita Imari</t>
-        </is>
-      </c>
-      <c r="K51" s="20" t="inlineStr">
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="K51" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -3681,39 +3690,39 @@
           <t>Chu Dau</t>
         </is>
       </c>
-      <c r="E52" s="18" t="inlineStr">
+      <c r="E52" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>Chu Dau</t>
-        </is>
-      </c>
-      <c r="G52" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G52" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
-          <t>Chu Dau</t>
-        </is>
-      </c>
-      <c r="I52" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I52" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>Chu Dau</t>
-        </is>
-      </c>
-      <c r="K52" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="K52" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -3736,37 +3745,37 @@
           <t>Chu Dau</t>
         </is>
       </c>
-      <c r="E53" s="18" t="inlineStr">
+      <c r="E53" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>Không xác định</t>
-        </is>
-      </c>
-      <c r="G53" s="20" t="inlineStr">
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G53" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
-          <t>Bien Hoa</t>
-        </is>
-      </c>
-      <c r="I53" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I53" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="J53" s="9" t="inlineStr">
         <is>
-          <t>Goryeo Celadon</t>
-        </is>
-      </c>
-      <c r="K53" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="K53" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -3788,42 +3797,42 @@
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Không xác định</t>
-        </is>
-      </c>
-      <c r="E54" s="21" t="inlineStr">
-        <is>
-          <t>SAI</t>
+          <t>Goryeo Celadon</t>
+        </is>
+      </c>
+      <c r="E54" s="19" t="inlineStr">
+        <is>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F54" s="9" t="inlineStr">
         <is>
-          <t>Meissen</t>
-        </is>
-      </c>
-      <c r="G54" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="G54" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="H54" s="9" t="inlineStr">
         <is>
-          <t>Goryeo Celadon</t>
-        </is>
-      </c>
-      <c r="I54" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I54" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>Goryeo Celadon</t>
-        </is>
-      </c>
-      <c r="K54" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="K54" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -3846,39 +3855,39 @@
           <t>Goryeo Celadon</t>
         </is>
       </c>
-      <c r="E55" s="18" t="inlineStr">
+      <c r="E55" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>Goryeo Celadon</t>
-        </is>
-      </c>
-      <c r="G55" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G55" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="H55" s="9" t="inlineStr">
         <is>
-          <t>Arita Imari</t>
-        </is>
-      </c>
-      <c r="I55" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I55" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
-          <t>Goryeo Celadon</t>
-        </is>
-      </c>
-      <c r="K55" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="K55" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -3901,37 +3910,37 @@
           <t>Goryeo Celadon</t>
         </is>
       </c>
-      <c r="E56" s="18" t="inlineStr">
+      <c r="E56" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F56" s="9" t="inlineStr">
         <is>
-          <t>Delftware</t>
-        </is>
-      </c>
-      <c r="G56" s="20" t="inlineStr">
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G56" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="H56" s="9" t="inlineStr">
         <is>
-          <t>Meissen</t>
-        </is>
-      </c>
-      <c r="I56" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I56" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="J56" s="9" t="inlineStr">
         <is>
-          <t>Arita Imari</t>
-        </is>
-      </c>
-      <c r="K56" s="20" t="inlineStr">
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="K56" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -3956,39 +3965,39 @@
           <t>Goryeo Celadon</t>
         </is>
       </c>
-      <c r="E57" s="18" t="inlineStr">
+      <c r="E57" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>Bien Hoa</t>
-        </is>
-      </c>
-      <c r="G57" s="20" t="inlineStr">
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G57" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I57" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J57" s="9" t="inlineStr">
+        <is>
           <t>Phu Lang</t>
         </is>
       </c>
-      <c r="I57" s="20" t="inlineStr">
-        <is>
-          <t>SAI</t>
-        </is>
-      </c>
-      <c r="J57" s="9" t="inlineStr">
-        <is>
-          <t>Goryeo Celadon</t>
-        </is>
-      </c>
-      <c r="K57" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+      <c r="K57" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4020,7 @@
           <t>Goryeo Celadon</t>
         </is>
       </c>
-      <c r="E58" s="18" t="inlineStr">
+      <c r="E58" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -4021,29 +4030,29 @@
           <t>Bat Trang</t>
         </is>
       </c>
-      <c r="G58" s="20" t="inlineStr">
+      <c r="G58" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
-          <t>Goryeo Celadon</t>
-        </is>
-      </c>
-      <c r="I58" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I58" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>Goryeo Celadon</t>
-        </is>
-      </c>
-      <c r="K58" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="K58" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -4066,37 +4075,37 @@
           <t>Goryeo Celadon</t>
         </is>
       </c>
-      <c r="E59" s="18" t="inlineStr">
+      <c r="E59" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>Goryeo Celadon</t>
-        </is>
-      </c>
-      <c r="G59" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="G59" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="H59" s="9" t="inlineStr">
         <is>
-          <t>Goryeo Celadon</t>
-        </is>
-      </c>
-      <c r="I59" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I59" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J59" s="9" t="inlineStr">
         <is>
-          <t>Delftware</t>
-        </is>
-      </c>
-      <c r="K59" s="20" t="inlineStr">
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="K59" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -4121,39 +4130,39 @@
           <t>Goryeo Celadon</t>
         </is>
       </c>
-      <c r="E60" s="18" t="inlineStr">
+      <c r="E60" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F60" s="9" t="inlineStr">
         <is>
-          <t>Iznik</t>
-        </is>
-      </c>
-      <c r="G60" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="G60" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
-          <t>Phu Lang</t>
-        </is>
-      </c>
-      <c r="I60" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I60" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>Goryeo Celadon</t>
-        </is>
-      </c>
-      <c r="K60" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="K60" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -4176,39 +4185,39 @@
           <t>Goryeo Celadon</t>
         </is>
       </c>
-      <c r="E61" s="18" t="inlineStr">
+      <c r="E61" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F61" s="9" t="inlineStr">
         <is>
-          <t>Meissen</t>
-        </is>
-      </c>
-      <c r="G61" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="G61" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
-          <t>Bien Hoa</t>
-        </is>
-      </c>
-      <c r="I61" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I61" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="J61" s="9" t="inlineStr">
         <is>
-          <t>Goryeo Celadon</t>
-        </is>
-      </c>
-      <c r="K61" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="K61" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -4231,27 +4240,27 @@
           <t>Goryeo Celadon</t>
         </is>
       </c>
-      <c r="E62" s="18" t="inlineStr">
+      <c r="E62" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>Chu Dau</t>
+          <t>Goryeo Celadon</t>
         </is>
       </c>
       <c r="G62" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H62" s="9" t="inlineStr">
         <is>
-          <t>Phu Lang</t>
-        </is>
-      </c>
-      <c r="I62" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I62" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -4261,7 +4270,7 @@
           <t>Goryeo Celadon</t>
         </is>
       </c>
-      <c r="K62" s="19" t="inlineStr">
+      <c r="K62" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -4286,37 +4295,37 @@
           <t>Goryeo Celadon</t>
         </is>
       </c>
-      <c r="E63" s="18" t="inlineStr">
+      <c r="E63" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>Arita Imari</t>
-        </is>
-      </c>
-      <c r="G63" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="G63" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="H63" s="9" t="inlineStr">
         <is>
-          <t>Goryeo Celadon</t>
-        </is>
-      </c>
-      <c r="I63" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I63" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J63" s="9" t="inlineStr">
         <is>
-          <t>Bat Trang</t>
-        </is>
-      </c>
-      <c r="K63" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="K63" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -4341,27 +4350,27 @@
           <t>Arita Imari</t>
         </is>
       </c>
-      <c r="E64" s="18" t="inlineStr">
+      <c r="E64" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F64" s="9" t="inlineStr">
         <is>
-          <t>Arita Imari</t>
-        </is>
-      </c>
-      <c r="G64" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="G64" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="H64" s="9" t="inlineStr">
         <is>
-          <t>Iznik</t>
-        </is>
-      </c>
-      <c r="I64" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I64" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -4371,7 +4380,7 @@
           <t>Không xác định</t>
         </is>
       </c>
-      <c r="K64" s="20" t="inlineStr">
+      <c r="K64" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -4396,7 +4405,7 @@
           <t>Arita Imari</t>
         </is>
       </c>
-      <c r="E65" s="18" t="inlineStr">
+      <c r="E65" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -4406,17 +4415,17 @@
           <t>Arita Imari</t>
         </is>
       </c>
-      <c r="G65" s="19" t="inlineStr">
+      <c r="G65" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H65" s="9" t="inlineStr">
         <is>
-          <t>Chu Dau</t>
-        </is>
-      </c>
-      <c r="I65" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I65" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -4426,7 +4435,7 @@
           <t>Arita Imari</t>
         </is>
       </c>
-      <c r="K65" s="19" t="inlineStr">
+      <c r="K65" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -4451,7 +4460,7 @@
           <t>Arita Imari</t>
         </is>
       </c>
-      <c r="E66" s="18" t="inlineStr">
+      <c r="E66" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -4461,27 +4470,27 @@
           <t>Arita Imari</t>
         </is>
       </c>
-      <c r="G66" s="19" t="inlineStr">
+      <c r="G66" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H66" s="9" t="inlineStr">
         <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I66" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="inlineStr">
+        <is>
           <t>Arita Imari</t>
         </is>
       </c>
-      <c r="I66" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="J66" s="9" t="inlineStr">
-        <is>
-          <t>Arita Imari</t>
-        </is>
-      </c>
-      <c r="K66" s="19" t="inlineStr">
+      <c r="K66" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -4506,7 +4515,7 @@
           <t>Arita Imari</t>
         </is>
       </c>
-      <c r="E67" s="18" t="inlineStr">
+      <c r="E67" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -4516,27 +4525,27 @@
           <t>Arita Imari</t>
         </is>
       </c>
-      <c r="G67" s="19" t="inlineStr">
+      <c r="G67" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H67" s="9" t="inlineStr">
         <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I67" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="inlineStr">
+        <is>
           <t>Arita Imari</t>
         </is>
       </c>
-      <c r="I67" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="J67" s="9" t="inlineStr">
-        <is>
-          <t>Arita Imari</t>
-        </is>
-      </c>
-      <c r="K67" s="19" t="inlineStr">
+      <c r="K67" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -4561,7 +4570,7 @@
           <t>Arita Imari</t>
         </is>
       </c>
-      <c r="E68" s="18" t="inlineStr">
+      <c r="E68" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -4571,29 +4580,29 @@
           <t>Arita Imari</t>
         </is>
       </c>
-      <c r="G68" s="19" t="inlineStr">
+      <c r="G68" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H68" s="9" t="inlineStr">
         <is>
-          <t>Chu Dau</t>
-        </is>
-      </c>
-      <c r="I68" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I68" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="J68" s="9" t="inlineStr">
         <is>
-          <t>Arita Imari</t>
-        </is>
-      </c>
-      <c r="K68" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="K68" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4625,7 @@
           <t>Arita Imari</t>
         </is>
       </c>
-      <c r="E69" s="18" t="inlineStr">
+      <c r="E69" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -4626,17 +4635,17 @@
           <t>Arita Imari</t>
         </is>
       </c>
-      <c r="G69" s="19" t="inlineStr">
+      <c r="G69" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H69" s="9" t="inlineStr">
         <is>
-          <t>Phu Lang</t>
-        </is>
-      </c>
-      <c r="I69" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I69" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -4646,7 +4655,7 @@
           <t>Arita Imari</t>
         </is>
       </c>
-      <c r="K69" s="19" t="inlineStr">
+      <c r="K69" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -4671,7 +4680,7 @@
           <t>Arita Imari</t>
         </is>
       </c>
-      <c r="E70" s="18" t="inlineStr">
+      <c r="E70" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -4681,17 +4690,17 @@
           <t>Arita Imari</t>
         </is>
       </c>
-      <c r="G70" s="19" t="inlineStr">
+      <c r="G70" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H70" s="9" t="inlineStr">
         <is>
-          <t>Bien Hoa</t>
-        </is>
-      </c>
-      <c r="I70" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I70" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -4701,7 +4710,7 @@
           <t>Arita Imari</t>
         </is>
       </c>
-      <c r="K70" s="19" t="inlineStr">
+      <c r="K70" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -4726,39 +4735,39 @@
           <t>Arita Imari</t>
         </is>
       </c>
-      <c r="E71" s="18" t="inlineStr">
+      <c r="E71" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F71" s="9" t="inlineStr">
         <is>
-          <t>Bau Truc</t>
+          <t>Arita Imari</t>
         </is>
       </c>
       <c r="G71" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H71" s="9" t="inlineStr">
         <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I71" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="inlineStr">
+        <is>
           <t>Arita Imari</t>
         </is>
       </c>
-      <c r="I71" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="J71" s="9" t="inlineStr">
-        <is>
-          <t>Meissen</t>
-        </is>
-      </c>
       <c r="K71" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
     </row>
@@ -4781,37 +4790,37 @@
           <t>Arita Imari</t>
         </is>
       </c>
-      <c r="E72" s="18" t="inlineStr">
+      <c r="E72" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>Bat Trang</t>
+          <t>Arita Imari</t>
         </is>
       </c>
       <c r="G72" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H72" s="9" t="inlineStr">
         <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I72" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="inlineStr">
+        <is>
           <t>Arita Imari</t>
         </is>
       </c>
-      <c r="I72" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="J72" s="9" t="inlineStr">
-        <is>
-          <t>Arita Imari</t>
-        </is>
-      </c>
-      <c r="K72" s="19" t="inlineStr">
+      <c r="K72" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -4833,12 +4842,12 @@
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Phu Lang</t>
-        </is>
-      </c>
-      <c r="E73" s="21" t="inlineStr">
-        <is>
-          <t>SAI</t>
+          <t>Arita Imari</t>
+        </is>
+      </c>
+      <c r="E73" s="19" t="inlineStr">
+        <is>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F73" s="9" t="inlineStr">
@@ -4846,27 +4855,27 @@
           <t>Arita Imari</t>
         </is>
       </c>
-      <c r="G73" s="19" t="inlineStr">
+      <c r="G73" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H73" s="9" t="inlineStr">
         <is>
-          <t>Phu Lang</t>
-        </is>
-      </c>
-      <c r="I73" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I73" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="J73" s="9" t="inlineStr">
         <is>
-          <t>Bat Trang</t>
-        </is>
-      </c>
-      <c r="K73" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="K73" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -4891,7 +4900,7 @@
           <t>Delftware</t>
         </is>
       </c>
-      <c r="E74" s="18" t="inlineStr">
+      <c r="E74" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -4901,27 +4910,27 @@
           <t>Delftware</t>
         </is>
       </c>
-      <c r="G74" s="19" t="inlineStr">
+      <c r="G74" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H74" s="9" t="inlineStr">
         <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I74" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="inlineStr">
+        <is>
           <t>Delftware</t>
         </is>
       </c>
-      <c r="I74" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="J74" s="9" t="inlineStr">
-        <is>
-          <t>Delftware</t>
-        </is>
-      </c>
-      <c r="K74" s="19" t="inlineStr">
+      <c r="K74" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -4946,39 +4955,39 @@
           <t>Delftware</t>
         </is>
       </c>
-      <c r="E75" s="18" t="inlineStr">
+      <c r="E75" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F75" s="9" t="inlineStr">
         <is>
-          <t>Arita Imari</t>
+          <t>Delftware</t>
         </is>
       </c>
       <c r="G75" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H75" s="9" t="inlineStr">
         <is>
-          <t>Phu Lang</t>
-        </is>
-      </c>
-      <c r="I75" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I75" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="J75" s="9" t="inlineStr">
         <is>
-          <t>Delftware</t>
-        </is>
-      </c>
-      <c r="K75" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="K75" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5010,7 @@
           <t>Delftware</t>
         </is>
       </c>
-      <c r="E76" s="18" t="inlineStr">
+      <c r="E76" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -5011,27 +5020,27 @@
           <t>Delftware</t>
         </is>
       </c>
-      <c r="G76" s="19" t="inlineStr">
+      <c r="G76" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H76" s="9" t="inlineStr">
         <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I76" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="inlineStr">
+        <is>
           <t>Delftware</t>
         </is>
       </c>
-      <c r="I76" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="J76" s="9" t="inlineStr">
-        <is>
-          <t>Delftware</t>
-        </is>
-      </c>
-      <c r="K76" s="19" t="inlineStr">
+      <c r="K76" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -5056,39 +5065,39 @@
           <t>Delftware</t>
         </is>
       </c>
-      <c r="E77" s="18" t="inlineStr">
+      <c r="E77" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>Iznik</t>
+          <t>Delftware</t>
         </is>
       </c>
       <c r="G77" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H77" s="9" t="inlineStr">
         <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I77" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J77" s="9" t="inlineStr">
+        <is>
           <t>Delftware</t>
         </is>
       </c>
-      <c r="I77" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="J77" s="9" t="inlineStr">
-        <is>
-          <t>Bau Truc</t>
-        </is>
-      </c>
       <c r="K77" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
     </row>
@@ -5111,39 +5120,39 @@
           <t>Delftware</t>
         </is>
       </c>
-      <c r="E78" s="18" t="inlineStr">
+      <c r="E78" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>Bien Hoa</t>
-        </is>
-      </c>
-      <c r="G78" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="G78" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="H78" s="9" t="inlineStr">
         <is>
-          <t>Delftware</t>
-        </is>
-      </c>
-      <c r="I78" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I78" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J78" s="9" t="inlineStr">
         <is>
-          <t>Delftware</t>
-        </is>
-      </c>
-      <c r="K78" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="K78" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5175,7 @@
           <t>Delftware</t>
         </is>
       </c>
-      <c r="E79" s="18" t="inlineStr">
+      <c r="E79" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -5176,29 +5185,29 @@
           <t>Delftware</t>
         </is>
       </c>
-      <c r="G79" s="19" t="inlineStr">
+      <c r="G79" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H79" s="9" t="inlineStr">
         <is>
-          <t>Iznik</t>
-        </is>
-      </c>
-      <c r="I79" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I79" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="J79" s="9" t="inlineStr">
         <is>
-          <t>Delftware</t>
-        </is>
-      </c>
-      <c r="K79" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="K79" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -5221,39 +5230,39 @@
           <t>Delftware</t>
         </is>
       </c>
-      <c r="E80" s="18" t="inlineStr">
+      <c r="E80" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>Bien Hoa</t>
+          <t>Delftware</t>
         </is>
       </c>
       <c r="G80" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H80" s="9" t="inlineStr">
         <is>
-          <t>Delftware</t>
-        </is>
-      </c>
-      <c r="I80" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I80" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J80" s="9" t="inlineStr">
         <is>
-          <t>Delftware</t>
-        </is>
-      </c>
-      <c r="K80" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="K80" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5285,7 @@
           <t>Delftware</t>
         </is>
       </c>
-      <c r="E81" s="18" t="inlineStr">
+      <c r="E81" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -5286,29 +5295,29 @@
           <t>Delftware</t>
         </is>
       </c>
-      <c r="G81" s="19" t="inlineStr">
+      <c r="G81" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H81" s="9" t="inlineStr">
         <is>
-          <t>Delftware</t>
-        </is>
-      </c>
-      <c r="I81" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I81" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J81" s="9" t="inlineStr">
         <is>
-          <t>Delftware</t>
-        </is>
-      </c>
-      <c r="K81" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="K81" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5340,7 @@
           <t>Delftware</t>
         </is>
       </c>
-      <c r="E82" s="18" t="inlineStr">
+      <c r="E82" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -5341,17 +5350,17 @@
           <t>Delftware</t>
         </is>
       </c>
-      <c r="G82" s="19" t="inlineStr">
+      <c r="G82" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H82" s="9" t="inlineStr">
         <is>
-          <t>Bien Hoa</t>
-        </is>
-      </c>
-      <c r="I82" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I82" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -5361,7 +5370,7 @@
           <t>Delftware</t>
         </is>
       </c>
-      <c r="K82" s="19" t="inlineStr">
+      <c r="K82" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -5386,7 +5395,7 @@
           <t>Delftware</t>
         </is>
       </c>
-      <c r="E83" s="18" t="inlineStr">
+      <c r="E83" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -5396,29 +5405,29 @@
           <t>Delftware</t>
         </is>
       </c>
-      <c r="G83" s="19" t="inlineStr">
+      <c r="G83" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H83" s="9" t="inlineStr">
         <is>
-          <t>Iznik</t>
-        </is>
-      </c>
-      <c r="I83" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I83" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="J83" s="9" t="inlineStr">
         <is>
-          <t>Bau Truc</t>
+          <t>Delftware</t>
         </is>
       </c>
       <c r="K83" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5450,7 @@
           <t>Iznik</t>
         </is>
       </c>
-      <c r="E84" s="18" t="inlineStr">
+      <c r="E84" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -5451,17 +5460,17 @@
           <t>Iznik</t>
         </is>
       </c>
-      <c r="G84" s="19" t="inlineStr">
+      <c r="G84" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H84" s="9" t="inlineStr">
         <is>
-          <t>Chu Dau</t>
-        </is>
-      </c>
-      <c r="I84" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I84" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -5471,7 +5480,7 @@
           <t>Iznik</t>
         </is>
       </c>
-      <c r="K84" s="19" t="inlineStr">
+      <c r="K84" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -5496,39 +5505,39 @@
           <t>Iznik</t>
         </is>
       </c>
-      <c r="E85" s="18" t="inlineStr">
+      <c r="E85" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr">
         <is>
-          <t>Iznik</t>
-        </is>
-      </c>
-      <c r="G85" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Jingdezhen</t>
+        </is>
+      </c>
+      <c r="G85" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="H85" s="9" t="inlineStr">
         <is>
-          <t>Phu Lang</t>
-        </is>
-      </c>
-      <c r="I85" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I85" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="J85" s="9" t="inlineStr">
         <is>
-          <t>Iznik</t>
-        </is>
-      </c>
-      <c r="K85" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Jingdezhen</t>
+        </is>
+      </c>
+      <c r="K85" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -5551,39 +5560,39 @@
           <t>Iznik</t>
         </is>
       </c>
-      <c r="E86" s="18" t="inlineStr">
+      <c r="E86" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>Không xác định</t>
+          <t>Iznik</t>
         </is>
       </c>
       <c r="G86" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H86" s="9" t="inlineStr">
         <is>
-          <t>Bat Trang</t>
-        </is>
-      </c>
-      <c r="I86" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I86" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="J86" s="9" t="inlineStr">
         <is>
-          <t>Delftware</t>
+          <t>Iznik</t>
         </is>
       </c>
       <c r="K86" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5615,7 @@
           <t>Iznik</t>
         </is>
       </c>
-      <c r="E87" s="18" t="inlineStr">
+      <c r="E87" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -5616,7 +5625,7 @@
           <t>Iznik</t>
         </is>
       </c>
-      <c r="G87" s="19" t="inlineStr">
+      <c r="G87" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -5626,7 +5635,7 @@
           <t>Không xác định</t>
         </is>
       </c>
-      <c r="I87" s="20" t="inlineStr">
+      <c r="I87" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -5636,7 +5645,7 @@
           <t>Iznik</t>
         </is>
       </c>
-      <c r="K87" s="19" t="inlineStr">
+      <c r="K87" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -5661,7 +5670,7 @@
           <t>Iznik</t>
         </is>
       </c>
-      <c r="E88" s="18" t="inlineStr">
+      <c r="E88" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -5671,27 +5680,27 @@
           <t>Iznik</t>
         </is>
       </c>
-      <c r="G88" s="19" t="inlineStr">
+      <c r="G88" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H88" s="9" t="inlineStr">
         <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I88" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J88" s="9" t="inlineStr">
+        <is>
           <t>Iznik</t>
         </is>
       </c>
-      <c r="I88" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="J88" s="9" t="inlineStr">
-        <is>
-          <t>Iznik</t>
-        </is>
-      </c>
-      <c r="K88" s="19" t="inlineStr">
+      <c r="K88" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -5716,37 +5725,37 @@
           <t>Iznik</t>
         </is>
       </c>
-      <c r="E89" s="18" t="inlineStr">
+      <c r="E89" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F89" s="9" t="inlineStr">
         <is>
-          <t>Meissen</t>
-        </is>
-      </c>
-      <c r="G89" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="G89" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="H89" s="9" t="inlineStr">
         <is>
-          <t>Iznik</t>
-        </is>
-      </c>
-      <c r="I89" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I89" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J89" s="9" t="inlineStr">
         <is>
-          <t>Goryeo Celadon</t>
-        </is>
-      </c>
-      <c r="K89" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="K89" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -5771,39 +5780,39 @@
           <t>Iznik</t>
         </is>
       </c>
-      <c r="E90" s="18" t="inlineStr">
+      <c r="E90" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F90" s="9" t="inlineStr">
         <is>
-          <t>Iznik</t>
-        </is>
-      </c>
-      <c r="G90" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="G90" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="H90" s="9" t="inlineStr">
         <is>
-          <t>Iznik</t>
-        </is>
-      </c>
-      <c r="I90" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I90" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J90" s="9" t="inlineStr">
         <is>
-          <t>Iznik</t>
-        </is>
-      </c>
-      <c r="K90" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Phu Lang</t>
+        </is>
+      </c>
+      <c r="K90" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -5826,39 +5835,39 @@
           <t>Iznik</t>
         </is>
       </c>
-      <c r="E91" s="18" t="inlineStr">
+      <c r="E91" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F91" s="9" t="inlineStr">
         <is>
-          <t>Bat Trang</t>
+          <t>Iznik</t>
         </is>
       </c>
       <c r="G91" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H91" s="9" t="inlineStr">
         <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I91" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J91" s="9" t="inlineStr">
+        <is>
           <t>Iznik</t>
         </is>
       </c>
-      <c r="I91" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="J91" s="9" t="inlineStr">
-        <is>
-          <t>Bau Truc</t>
-        </is>
-      </c>
       <c r="K91" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5890,7 @@
           <t>Iznik</t>
         </is>
       </c>
-      <c r="E92" s="18" t="inlineStr">
+      <c r="E92" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -5891,27 +5900,27 @@
           <t>Iznik</t>
         </is>
       </c>
-      <c r="G92" s="19" t="inlineStr">
+      <c r="G92" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H92" s="9" t="inlineStr">
         <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I92" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J92" s="9" t="inlineStr">
+        <is>
           <t>Iznik</t>
         </is>
       </c>
-      <c r="I92" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="J92" s="9" t="inlineStr">
-        <is>
-          <t>Iznik</t>
-        </is>
-      </c>
-      <c r="K92" s="19" t="inlineStr">
+      <c r="K92" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -5933,40 +5942,40 @@
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Phu Lang</t>
-        </is>
-      </c>
-      <c r="E93" s="21" t="inlineStr">
-        <is>
-          <t>SAI</t>
+          <t>Iznik</t>
+        </is>
+      </c>
+      <c r="E93" s="19" t="inlineStr">
+        <is>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F93" s="9" t="inlineStr">
         <is>
-          <t>Iznik</t>
-        </is>
-      </c>
-      <c r="G93" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="G93" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="H93" s="9" t="inlineStr">
         <is>
-          <t>Bat Trang</t>
-        </is>
-      </c>
-      <c r="I93" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I93" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="J93" s="9" t="inlineStr">
         <is>
-          <t>Goryeo Celadon</t>
-        </is>
-      </c>
-      <c r="K93" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="K93" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -5991,39 +6000,39 @@
           <t>Meissen</t>
         </is>
       </c>
-      <c r="E94" s="18" t="inlineStr">
+      <c r="E94" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>Chu Dau</t>
+          <t>Meissen</t>
         </is>
       </c>
       <c r="G94" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H94" s="9" t="inlineStr">
         <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I94" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="inlineStr">
+        <is>
           <t>Meissen</t>
         </is>
       </c>
-      <c r="I94" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="J94" s="9" t="inlineStr">
-        <is>
-          <t>Không xác định</t>
-        </is>
-      </c>
       <c r="K94" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6055,7 @@
           <t>Meissen</t>
         </is>
       </c>
-      <c r="E95" s="18" t="inlineStr">
+      <c r="E95" s="19" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -6056,27 +6065,27 @@
           <t>Meissen</t>
         </is>
       </c>
-      <c r="G95" s="19" t="inlineStr">
+      <c r="G95" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H95" s="9" t="inlineStr">
         <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I95" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="inlineStr">
+        <is>
           <t>Meissen</t>
         </is>
       </c>
-      <c r="I95" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="J95" s="9" t="inlineStr">
-        <is>
-          <t>Meissen</t>
-        </is>
-      </c>
-      <c r="K95" s="19" t="inlineStr">
+      <c r="K95" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -6098,30 +6107,30 @@
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="E96" s="22" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
           <t>Meissen</t>
         </is>
       </c>
-      <c r="E96" s="18" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="F96" s="9" t="inlineStr">
-        <is>
-          <t>Goryeo Celadon</t>
-        </is>
-      </c>
       <c r="G96" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H96" s="9" t="inlineStr">
         <is>
-          <t>Phu Lang</t>
-        </is>
-      </c>
-      <c r="I96" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I96" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -6131,7 +6140,7 @@
           <t>Meissen</t>
         </is>
       </c>
-      <c r="K96" s="19" t="inlineStr">
+      <c r="K96" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -6153,40 +6162,40 @@
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="E97" s="22" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
           <t>Meissen</t>
         </is>
       </c>
-      <c r="E97" s="18" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="F97" s="9" t="inlineStr">
+      <c r="G97" s="20" t="inlineStr">
+        <is>
+          <t>ĐÚNG</t>
+        </is>
+      </c>
+      <c r="H97" s="9" t="inlineStr">
+        <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I97" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="inlineStr">
         <is>
           <t>Meissen</t>
         </is>
       </c>
-      <c r="G97" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="H97" s="9" t="inlineStr">
-        <is>
-          <t>Meissen</t>
-        </is>
-      </c>
-      <c r="I97" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="J97" s="9" t="inlineStr">
-        <is>
-          <t>Meissen</t>
-        </is>
-      </c>
-      <c r="K97" s="19" t="inlineStr">
+      <c r="K97" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -6208,30 +6217,30 @@
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="E98" s="22" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
           <t>Meissen</t>
         </is>
       </c>
-      <c r="E98" s="18" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="F98" s="9" t="inlineStr">
-        <is>
-          <t>Bat Trang</t>
-        </is>
-      </c>
       <c r="G98" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H98" s="9" t="inlineStr">
         <is>
-          <t>Bat Trang</t>
-        </is>
-      </c>
-      <c r="I98" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I98" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
@@ -6241,7 +6250,7 @@
           <t>Meissen</t>
         </is>
       </c>
-      <c r="K98" s="19" t="inlineStr">
+      <c r="K98" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -6263,40 +6272,40 @@
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="E99" s="22" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
           <t>Meissen</t>
         </is>
       </c>
-      <c r="E99" s="18" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="F99" s="9" t="inlineStr">
-        <is>
-          <t>Bau Truc</t>
-        </is>
-      </c>
       <c r="G99" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H99" s="9" t="inlineStr">
         <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I99" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="inlineStr">
+        <is>
           <t>Meissen</t>
         </is>
       </c>
-      <c r="I99" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="J99" s="9" t="inlineStr">
-        <is>
-          <t>Meissen</t>
-        </is>
-      </c>
-      <c r="K99" s="19" t="inlineStr">
+      <c r="K99" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -6318,40 +6327,40 @@
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="E100" s="22" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
           <t>Meissen</t>
         </is>
       </c>
-      <c r="E100" s="18" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="F100" s="9" t="inlineStr">
+      <c r="G100" s="20" t="inlineStr">
+        <is>
+          <t>ĐÚNG</t>
+        </is>
+      </c>
+      <c r="H100" s="9" t="inlineStr">
+        <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I100" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="inlineStr">
         <is>
           <t>Meissen</t>
         </is>
       </c>
-      <c r="G100" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="H100" s="9" t="inlineStr">
-        <is>
-          <t>Bat Trang</t>
-        </is>
-      </c>
-      <c r="I100" s="20" t="inlineStr">
-        <is>
-          <t>SAI</t>
-        </is>
-      </c>
-      <c r="J100" s="9" t="inlineStr">
-        <is>
-          <t>Meissen</t>
-        </is>
-      </c>
-      <c r="K100" s="19" t="inlineStr">
+      <c r="K100" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -6373,40 +6382,40 @@
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="E101" s="22" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
           <t>Meissen</t>
         </is>
       </c>
-      <c r="E101" s="18" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="F101" s="9" t="inlineStr">
+      <c r="G101" s="20" t="inlineStr">
+        <is>
+          <t>ĐÚNG</t>
+        </is>
+      </c>
+      <c r="H101" s="9" t="inlineStr">
+        <is>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I101" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="inlineStr">
         <is>
           <t>Meissen</t>
         </is>
       </c>
-      <c r="G101" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-      <c r="H101" s="9" t="inlineStr">
-        <is>
-          <t>Iznik</t>
-        </is>
-      </c>
-      <c r="I101" s="20" t="inlineStr">
-        <is>
-          <t>SAI</t>
-        </is>
-      </c>
-      <c r="J101" s="9" t="inlineStr">
-        <is>
-          <t>Meissen</t>
-        </is>
-      </c>
-      <c r="K101" s="19" t="inlineStr">
+      <c r="K101" s="20" t="inlineStr">
         <is>
           <t>ĐÚNG</t>
         </is>
@@ -6428,42 +6437,42 @@
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Không xác định</t>
-        </is>
-      </c>
-      <c r="E102" s="21" t="inlineStr">
+          <t>Bat Trang</t>
+        </is>
+      </c>
+      <c r="E102" s="22" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
       </c>
       <c r="F102" s="9" t="inlineStr">
         <is>
-          <t>Bien Hoa</t>
+          <t>Meissen</t>
         </is>
       </c>
       <c r="G102" s="20" t="inlineStr">
         <is>
-          <t>SAI</t>
+          <t>ĐÚNG</t>
         </is>
       </c>
       <c r="H102" s="9" t="inlineStr">
         <is>
-          <t>Meissen</t>
-        </is>
-      </c>
-      <c r="I102" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I102" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J102" s="9" t="inlineStr">
         <is>
-          <t>Meissen</t>
-        </is>
-      </c>
-      <c r="K102" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="K102" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
     </row>
@@ -6483,40 +6492,40 @@
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Meissen</t>
-        </is>
-      </c>
-      <c r="E103" s="18" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="E103" s="22" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="F103" s="9" t="inlineStr">
         <is>
-          <t>Meissen</t>
-        </is>
-      </c>
-      <c r="G103" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="G103" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="H103" s="9" t="inlineStr">
         <is>
-          <t>Meissen</t>
-        </is>
-      </c>
-      <c r="I103" s="19" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="I103" s="21" t="inlineStr">
+        <is>
+          <t>SAI</t>
         </is>
       </c>
       <c r="J103" s="9" t="inlineStr">
         <is>
-          <t>Bien Hoa</t>
-        </is>
-      </c>
-      <c r="K103" s="20" t="inlineStr">
+          <t>Không xác định</t>
+        </is>
+      </c>
+      <c r="K103" s="21" t="inlineStr">
         <is>
           <t>SAI</t>
         </is>
